--- a/output/pdf_financials_xlsx/EMET.xlsx
+++ b/output/pdf_financials_xlsx/EMET.xlsx
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.258577</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.203515</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.159239</v>
       </c>
     </row>
     <row r="35">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.258577</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.203515</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.159239</v>
       </c>
     </row>
     <row r="37">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.261247</v>
+        <v>0.00267</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.207346</v>
+        <v>0.003831</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.159239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMET.xlsx
+++ b/output/pdf_financials_xlsx/EMET.xlsx
@@ -2506,20 +2506,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.141566</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.045826</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.044722</v>
       </c>
     </row>
     <row r="100">
@@ -2533,20 +2527,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2560,20 +2548,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.001866</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.001239</v>
       </c>
     </row>
     <row r="102">
@@ -2587,20 +2569,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2614,20 +2590,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>-0.00267</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.001161</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.003831</v>
       </c>
     </row>
     <row r="104">
@@ -2641,20 +2611,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.010924</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>-0.006209</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.004624</v>
       </c>
     </row>
     <row r="105">
@@ -2668,20 +2632,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2695,20 +2653,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.001914</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.009235999999999999</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.000446</v>
       </c>
     </row>
     <row r="107">
@@ -2722,20 +2674,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2749,20 +2695,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2776,20 +2716,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2803,20 +2737,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2830,20 +2758,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2857,20 +2779,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2884,20 +2800,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2911,20 +2821,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2938,20 +2842,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2965,20 +2863,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2992,20 +2884,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3019,20 +2905,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3073,20 +2953,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3100,20 +2974,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3127,20 +2995,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3154,20 +3016,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3181,20 +3037,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3208,20 +3058,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3235,20 +3079,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3289,20 +3127,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3343,20 +3175,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0.398229</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.258577</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.203515</v>
       </c>
     </row>
     <row r="131">
@@ -3370,20 +3196,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3397,20 +3217,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>-0.139652</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.055062</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.044276</v>
       </c>
     </row>
     <row r="133">
@@ -3424,20 +3238,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.258577</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.203515</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.159239</v>
       </c>
     </row>
     <row r="134">
@@ -3451,20 +3259,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3478,20 +3280,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-0.139652</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.055062</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.044276</v>
       </c>
     </row>
   </sheetData>
@@ -3505,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4033,22 +3829,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4057,34 +3853,34 @@
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.001347</v>
+        <v>-0.141566</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.001415</v>
+        <v>-0.045826</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.001302</v>
+        <v>-0.044722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Professional fees (Note 6)</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4093,66 +3889,70 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.035565</v>
+        <v>-0.00267</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.024373</v>
+        <v>-0.001161</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.029809</v>
+        <v>0.003831</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Regulatory and filing</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.021473</v>
+        <v>-0.00634</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.020038</v>
+        <v>-0.001866</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.013611</v>
+        <v>0.001239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4161,34 +3961,34 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.141566</v>
+        <v>0.010924</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.045826</v>
+        <v>-0.006209</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.044722</v>
+        <v>-0.004624</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Net cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4197,34 +3997,34 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>-0.139652</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>-0.055062</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>-0.044276</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4233,68 +4033,70 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>32.959282</v>
+        <v>-0.139652</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>32.959282</v>
+        <v>-0.055062</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>32.959282</v>
+        <v>-0.044276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Issued        Share Capital         Deficit                 Equity</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2023 32,959,282 790,829</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="5" t="n">
+        <v>0.398229</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.206586</v>
+        <v>0.258577</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-0.584243</v>
+        <v>0.203515</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Issued        Share Capital         Deficit                 Equity</t>
+          <t>Changes in non-cash working capital item</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Net loss for the year - -</t>
+          <t>Cash, end of the year</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4302,16 +4104,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="5" t="n">
+        <v>0.258577</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.045826</v>
+        <v>0.203515</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.045826</v>
+        <v>0.159239</v>
       </c>
     </row>
     <row r="23">
@@ -4322,30 +4122,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Issued        Share Capital         Deficit                 Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2024 32,959,282 790,829</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="5" t="n">
+        <v>0.001347</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.16076</v>
+        <v>0.001415</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-0.630069</v>
+        <v>0.001302</v>
       </c>
     </row>
     <row r="24">
@@ -4356,30 +4158,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Issued        Share Capital         Deficit                 Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2025 32,959,282 790,829</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Professional fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="5" t="n">
+        <v>0.035565</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.116038</v>
+        <v>0.024373</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-0.674791</v>
+        <v>0.029809</v>
       </c>
     </row>
     <row r="25">
@@ -4395,7 +4199,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Travel expenses</t>
+          <t>Regulatory and filing</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -4405,17 +4209,13 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.005681</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021473</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.020038</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.013611</v>
       </c>
     </row>
     <row r="26">
@@ -4431,12 +4231,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4445,17 +4245,13 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.141566</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.045826</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-0.044722</v>
       </c>
     </row>
     <row r="27">
@@ -4471,27 +4267,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Property investigation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4502,30 +4298,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Issued        Share Capital             Deficit              Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2022 32,959,282 790,829</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.348152</v>
+        <v>32.959282</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.442677</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.959282</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>32.959282</v>
       </c>
     </row>
     <row r="29">
@@ -4536,34 +4334,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Issued        Share Capital             Deficit              Equity</t>
+          <t>Issued        Share Capital         Deficit                 Equity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net loss for the year - -</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at April 30, 2023 32,959,282 790,829</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>-0.141566</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.141566</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.206586</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-0.584243</v>
       </c>
     </row>
     <row r="30">
@@ -4574,30 +4368,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Issued        Share Capital             Deficit              Equity</t>
+          <t>Issued        Share Capital         Deficit                 Equity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2023 32,959,282 790,829</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Net loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>0.206586</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.584243</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.045826</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.045826</v>
       </c>
     </row>
     <row r="31">
@@ -4608,7 +4406,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Issued        Share Capital             Deficit              Equity</t>
+          <t>Issued        Share Capital         Deficit                 Equity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4622,13 +4420,299 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>0.16076</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>-0.630069</v>
       </c>
-      <c r="H31" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Issued        Share Capital         Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Balance at April 30, 2025 32,959,282 790,829</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.116038</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>-0.674791</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Travel expenses</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.005681</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Issued        Share Capital             Deficit              Equity</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Balance at April 30, 2022 32,959,282 790,829</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.348152</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.442677</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Issued        Share Capital             Deficit              Equity</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Net loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-0.141566</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-0.141566</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Issued        Share Capital             Deficit              Equity</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Balance at April 30, 2023 32,959,282 790,829</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.206586</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.584243</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Issued        Share Capital             Deficit              Equity</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Balance at April 30, 2024 32,959,282 790,829</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.16076</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-0.630069</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
